--- a/RoboCerebrum/行为闭集设计.xlsx
+++ b/RoboCerebrum/行为闭集设计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="13200" windowHeight="8955" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="第一层-全屋级任务编排" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="144">
   <si>
     <t>本体移动类</t>
   </si>
@@ -49,10 +49,34 @@
     <t>打扫厨房</t>
   </si>
   <si>
-    <t>移动至卧室</t>
-  </si>
-  <si>
-    <t>打扫卧室</t>
+    <t>移动至主卧</t>
+  </si>
+  <si>
+    <t>打扫主卧</t>
+  </si>
+  <si>
+    <t>移动至次卧</t>
+  </si>
+  <si>
+    <t>打扫次卧</t>
+  </si>
+  <si>
+    <t>移动至儿童房</t>
+  </si>
+  <si>
+    <t>打扫儿童房</t>
+  </si>
+  <si>
+    <t>移动至餐厅</t>
+  </si>
+  <si>
+    <t>打扫餐厅</t>
+  </si>
+  <si>
+    <t>移动至洗衣房</t>
+  </si>
+  <si>
+    <t>打扫洗衣房</t>
   </si>
   <si>
     <t>移动至卫生间</t>
@@ -73,196 +97,370 @@
     <t>打扫书房</t>
   </si>
   <si>
-    <t>整理餐桌</t>
-  </si>
-  <si>
-    <t>整理书桌</t>
-  </si>
-  <si>
-    <t>整理床铺</t>
-  </si>
-  <si>
-    <t>整理沙发</t>
-  </si>
-  <si>
-    <t>整理厨房工作台</t>
+    <t>移动至储藏室</t>
+  </si>
+  <si>
+    <t>打扫储藏室</t>
+  </si>
+  <si>
+    <t>动作类</t>
+  </si>
+  <si>
+    <t>导航类</t>
+  </si>
+  <si>
+    <t>动作+导航类</t>
+  </si>
+  <si>
+    <t>摆放餐盘</t>
+  </si>
+  <si>
+    <t>导航至卧室门前</t>
+  </si>
+  <si>
+    <t>扔垃圾到垃圾桶</t>
+  </si>
+  <si>
+    <t>摆放水杯</t>
+  </si>
+  <si>
+    <t>进入卧室</t>
+  </si>
+  <si>
+    <t>挂衣服到晾衣架</t>
+  </si>
+  <si>
+    <t>摆放枕头</t>
+  </si>
+  <si>
+    <t>导航至厨房门前</t>
+  </si>
+  <si>
+    <t>洗碗</t>
+  </si>
+  <si>
+    <t>摆放水壶</t>
+  </si>
+  <si>
+    <t>进入厨房</t>
+  </si>
+  <si>
+    <t>铺床</t>
+  </si>
+  <si>
+    <t>摆放抹布</t>
+  </si>
+  <si>
+    <t>导航至客厅门前</t>
+  </si>
+  <si>
+    <t>摆放水果</t>
+  </si>
+  <si>
+    <t>进入客厅</t>
+  </si>
+  <si>
+    <t>摆放笔</t>
+  </si>
+  <si>
+    <t>导航至卫生间门前</t>
+  </si>
+  <si>
+    <t>摆放水瓶</t>
+  </si>
+  <si>
+    <t>进入卫生间</t>
+  </si>
+  <si>
+    <t>摆放椅子</t>
+  </si>
+  <si>
+    <t>导航至阳台门前</t>
+  </si>
+  <si>
+    <t>摆放书本</t>
+  </si>
+  <si>
+    <t>进入阳台</t>
+  </si>
+  <si>
+    <t>叠衣服</t>
+  </si>
+  <si>
+    <t>导航至书房门前</t>
+  </si>
+  <si>
+    <t>打开抽屉</t>
+  </si>
+  <si>
+    <t>进入书房</t>
+  </si>
+  <si>
+    <t>打开柜门</t>
+  </si>
+  <si>
+    <t>导航至床边</t>
+  </si>
+  <si>
+    <t>关闭抽屉</t>
+  </si>
+  <si>
+    <t>导航至地面垃圾前</t>
+  </si>
+  <si>
+    <t>关闭柜门</t>
+  </si>
+  <si>
+    <t>导航至书桌边</t>
   </si>
   <si>
     <t>拿取水杯</t>
   </si>
   <si>
+    <t>导航至餐桌边</t>
+  </si>
+  <si>
     <t>放置水杯</t>
   </si>
   <si>
+    <t>导航至沙发边</t>
+  </si>
+  <si>
     <t>拿取抹布</t>
   </si>
   <si>
+    <t>导航至洗手台边</t>
+  </si>
+  <si>
     <t>放置抹布</t>
   </si>
   <si>
+    <t>导航至床头柜前</t>
+  </si>
+  <si>
     <t>拿取箱子</t>
   </si>
   <si>
+    <t>导航至衣柜前</t>
+  </si>
+  <si>
     <t>放置箱子</t>
   </si>
   <si>
-    <t>动作类</t>
-  </si>
-  <si>
-    <t>导航类</t>
-  </si>
-  <si>
-    <t>动作+导航类</t>
-  </si>
-  <si>
-    <t>摆放餐盘</t>
-  </si>
-  <si>
-    <t>导航至卧室门前</t>
-  </si>
-  <si>
-    <t>扔垃圾</t>
-  </si>
-  <si>
-    <t>摆放水杯</t>
-  </si>
-  <si>
-    <t>进入卧室</t>
-  </si>
-  <si>
-    <t>挂衣服</t>
-  </si>
-  <si>
-    <t>摆放枕头</t>
-  </si>
-  <si>
-    <t>导航至厨房门前</t>
-  </si>
-  <si>
-    <t>洗碗</t>
-  </si>
-  <si>
-    <t>摆放水壶</t>
-  </si>
-  <si>
-    <t>进入厨房</t>
-  </si>
-  <si>
-    <t>铺床</t>
-  </si>
-  <si>
-    <t>摆放抹布</t>
-  </si>
-  <si>
-    <t>导航至客厅门前</t>
-  </si>
-  <si>
-    <t>摆放水果</t>
-  </si>
-  <si>
-    <t>进入客厅</t>
-  </si>
-  <si>
-    <t>摆放笔</t>
-  </si>
-  <si>
-    <t>导航至卫生间门前</t>
-  </si>
-  <si>
-    <t>摆放水瓶</t>
-  </si>
-  <si>
-    <t>进入卫生间</t>
-  </si>
-  <si>
-    <t>摆放椅子</t>
-  </si>
-  <si>
-    <t>导航至阳台门前</t>
-  </si>
-  <si>
-    <t>摆放书本</t>
-  </si>
-  <si>
-    <t>进入阳台</t>
-  </si>
-  <si>
-    <t>叠衣服</t>
-  </si>
-  <si>
-    <t>导航至书房门前</t>
-  </si>
-  <si>
-    <t>打开抽屉</t>
-  </si>
-  <si>
-    <t>进入书房</t>
-  </si>
-  <si>
-    <t>打开柜门</t>
-  </si>
-  <si>
-    <t>导航至床边</t>
-  </si>
-  <si>
-    <t>关闭抽屉</t>
-  </si>
-  <si>
-    <t>导航至地面垃圾前</t>
-  </si>
-  <si>
-    <t>关闭柜门</t>
-  </si>
-  <si>
-    <t>导航至书桌边</t>
-  </si>
-  <si>
-    <t>导航至餐桌边</t>
-  </si>
-  <si>
-    <t>导航至沙发边</t>
-  </si>
-  <si>
-    <t>导航至洗手台边</t>
-  </si>
-  <si>
-    <t>导航至床头柜前</t>
-  </si>
-  <si>
-    <t>导航至衣柜前</t>
-  </si>
-  <si>
     <t xml:space="preserve">导航至晾衣杆边 </t>
   </si>
   <si>
     <t>导航至水斗边</t>
   </si>
   <si>
-    <t>&lt;grasp&gt;（和小脑配合）</t>
+    <t>翻译</t>
+  </si>
+  <si>
+    <t>&lt;grasp&gt;</t>
+  </si>
+  <si>
+    <t>抓取</t>
   </si>
   <si>
     <t>&lt;navi&gt;</t>
   </si>
   <si>
-    <t>&lt;put&gt;</t>
-  </si>
-  <si>
-    <t>&lt;fold&gt;（和小脑结合）</t>
+    <t>&lt;place&gt;</t>
+  </si>
+  <si>
+    <t>放置</t>
   </si>
   <si>
     <t>&lt;move&gt;</t>
   </si>
   <si>
+    <t>移动</t>
+  </si>
+  <si>
     <t>&lt;push&gt;</t>
   </si>
   <si>
+    <t>推</t>
+  </si>
+  <si>
+    <t>&lt;pull&gt;</t>
+  </si>
+  <si>
+    <t>拉</t>
+  </si>
+  <si>
+    <t>&lt;fold&gt;</t>
+  </si>
+  <si>
+    <t>折叠</t>
+  </si>
+  <si>
+    <t>&lt;release&gt;</t>
+  </si>
+  <si>
+    <t>释放</t>
+  </si>
+  <si>
+    <t>&lt;press&gt;</t>
+  </si>
+  <si>
+    <t>压</t>
+  </si>
+  <si>
+    <t>&lt;tap&gt;</t>
+  </si>
+  <si>
+    <t>按</t>
+  </si>
+  <si>
     <t>&lt;rotate&gt;</t>
   </si>
   <si>
-    <t>&lt;press&gt;</t>
-  </si>
-  <si>
-    <t>&lt;pull&gt;</t>
+    <t>旋转</t>
+  </si>
+  <si>
+    <t>&lt;twist&gt;</t>
+  </si>
+  <si>
+    <t>扭</t>
+  </si>
+  <si>
+    <t>&lt;slide&gt;</t>
+  </si>
+  <si>
+    <t>滑动</t>
+  </si>
+  <si>
+    <t>&lt;sweep&gt;</t>
+  </si>
+  <si>
+    <t>扫</t>
+  </si>
+  <si>
+    <t>&lt;pick&gt;</t>
+  </si>
+  <si>
+    <t>摘</t>
+  </si>
+  <si>
+    <t>&lt;drop&gt;</t>
+  </si>
+  <si>
+    <t>扔</t>
+  </si>
+  <si>
+    <t>&lt;open&gt;</t>
+  </si>
+  <si>
+    <t>打开</t>
+  </si>
+  <si>
+    <t>&lt;close&gt;</t>
+  </si>
+  <si>
+    <t>关闭</t>
+  </si>
+  <si>
+    <t>&lt;wipe&gt;</t>
+  </si>
+  <si>
+    <t>擦拭</t>
+  </si>
+  <si>
+    <t>&lt;toggle on&gt;</t>
+  </si>
+  <si>
+    <t>打开开关</t>
+  </si>
+  <si>
+    <t>&lt;toggle off&gt;</t>
+  </si>
+  <si>
+    <t>关闭开关</t>
+  </si>
+  <si>
+    <t>&lt;pour&gt;</t>
+  </si>
+  <si>
+    <t>倾倒</t>
+  </si>
+  <si>
+    <t>&lt;scoop&gt;</t>
+  </si>
+  <si>
+    <t>用勺子挖</t>
+  </si>
+  <si>
+    <t>&lt;stir&gt;</t>
+  </si>
+  <si>
+    <t>搅拌</t>
+  </si>
+  <si>
+    <t>&lt;mix&gt;</t>
+  </si>
+  <si>
+    <t>混合</t>
+  </si>
+  <si>
+    <t>&lt;unfold&gt;</t>
+  </si>
+  <si>
+    <t>打开折叠</t>
+  </si>
+  <si>
+    <t>&lt;scrub&gt;</t>
+  </si>
+  <si>
+    <t>擦洗</t>
+  </si>
+  <si>
+    <t>&lt;peel&gt;</t>
+  </si>
+  <si>
+    <t>剥落</t>
+  </si>
+  <si>
+    <t>&lt;cut&gt;</t>
+  </si>
+  <si>
+    <t>切</t>
+  </si>
+  <si>
+    <t>&lt;plug in&gt;</t>
+  </si>
+  <si>
+    <t>插入</t>
+  </si>
+  <si>
+    <t>&lt;unplug&gt;</t>
+  </si>
+  <si>
+    <t>拔出</t>
+  </si>
+  <si>
+    <t>&lt;tie&gt;</t>
+  </si>
+  <si>
+    <t>系</t>
+  </si>
+  <si>
+    <t>&lt;untie&gt;</t>
+  </si>
+  <si>
+    <t>解开</t>
+  </si>
+  <si>
+    <t>&lt;spray&gt;</t>
+  </si>
+  <si>
+    <t>喷</t>
+  </si>
+  <si>
+    <t>&lt;dice&gt;</t>
+  </si>
+  <si>
+    <t>切块</t>
   </si>
 </sst>
 </file>
@@ -441,7 +639,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -451,12 +649,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -812,7 +1004,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -836,16 +1028,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="7">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
@@ -854,89 +1046,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -946,28 +1138,25 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1290,7 +1479,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="25.25" style="1" customWidth="1"/>
@@ -1306,108 +1495,109 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="21" spans="1:2">
-      <c r="B8" s="11" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="B9" s="3" t="s">
-        <v>15</v>
+      <c r="A9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="B10" s="3" t="s">
-        <v>16</v>
+      <c r="A10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="B11" s="3" t="s">
-        <v>17</v>
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="B12" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="B13" s="9" t="s">
-        <v>19</v>
-      </c>
+      <c r="A12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" ht="21" spans="1:2">
+      <c r="B13" s="10"/>
     </row>
     <row r="14" spans="1:2">
-      <c r="B14" s="9" t="s">
-        <v>20</v>
-      </c>
+      <c r="B14" s="4"/>
     </row>
     <row r="15" spans="1:2">
-      <c r="B15" s="9" t="s">
-        <v>21</v>
-      </c>
+      <c r="B15" s="4"/>
     </row>
     <row r="16" spans="1:2">
-      <c r="B16" s="9" t="s">
-        <v>22</v>
-      </c>
+      <c r="B16" s="4"/>
     </row>
     <row r="17" spans="2:2">
-      <c r="B17" s="10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2">
-      <c r="B18" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="24" ht="13.5"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1427,209 +1617,209 @@
   <sheetData>
     <row r="1" ht="21" spans="1:3">
       <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
+      <c r="B2" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="3"/>
+      <c r="C6" s="4"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="4"/>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="4"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="4"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="9" t="s">
-        <v>19</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="9" t="s">
-        <v>20</v>
+      <c r="A18" s="8" t="s">
+        <v>63</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="9" t="s">
-        <v>21</v>
+      <c r="A19" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="9" t="s">
-        <v>22</v>
+      <c r="A20" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="10" t="s">
-        <v>23</v>
+      <c r="A21" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="10" t="s">
-        <v>24</v>
+      <c r="A22" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="B23" s="7" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1642,91 +1832,314 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" outlineLevelCol="1"/>
+  <dimension ref="A1:C35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.25" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="27" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31.875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="27" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" spans="1:2">
+    <row r="1" ht="21" spans="1:3">
       <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>76</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="3"/>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="3"/>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="3"/>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="3"/>
-    </row>
-    <row r="8" spans="1:2">
+        <v>78</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="4"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="4"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="4"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="4"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="4"/>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" s="3"/>
-    </row>
-    <row r="9" spans="1:2">
+        <v>88</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="4"/>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="3"/>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="B10" s="3"/>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="B11" s="3"/>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="B12" s="3"/>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="B13" s="3"/>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="B14" s="3"/>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="B15" s="3"/>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="B16" s="3"/>
+        <v>90</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="4"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="4"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>143</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
